--- a/BOEproject/Tutorial/Sparkle/sparkle_database0608.xlsx
+++ b/BOEproject/Tutorial/Sparkle/sparkle_database0608.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PHD\GitFiles\diffractsim\BOEproject\test0427\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\Sparkle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B682DFD5-993B-492E-B7AE-FFB91A1E4731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CE696B5-44E7-42D3-BCD6-1CEEBBD70BDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15990" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-22770" yWindow="5145" windowWidth="21600" windowHeight="11505" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -43,25 +43,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image1.png</t>
-  </si>
-  <si>
     <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image2.png</t>
-  </si>
-  <si>
-    <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image3.png</t>
-  </si>
-  <si>
-    <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image4.png</t>
-  </si>
-  <si>
-    <t>F:\PHD\GitFiles\diffractsim\BOEproject\sparkle0511\image5.png</t>
-  </si>
-  <si>
     <t>B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -71,6 +56,26 @@
   </si>
   <si>
     <t>sample_id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image1.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image2.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image3.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image4.png</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>F:\PHD\GitFiles\diffractsim\BOEproject\Tutorial\imagefiles\image5.png</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -406,12 +411,12 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="45.9140625" customWidth="1"/>
+    <col min="2" max="2" width="52.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -426,7 +431,7 @@
         <v>3</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -434,7 +439,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" s="1">
         <v>-0.33900000000000002</v>
@@ -443,7 +448,7 @@
         <v>0.78</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" s="1">
         <v>1.5509999999999999</v>
@@ -454,7 +459,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1">
         <v>-0.503</v>
@@ -463,7 +468,7 @@
         <v>1.095</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F3" s="1">
         <v>2.073</v>
@@ -474,7 +479,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1">
         <v>-0.63500000000000001</v>
@@ -483,7 +488,7 @@
         <v>1.3009999999999999</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F4" s="1">
         <v>2.1440000000000001</v>
@@ -494,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>-0.92500000000000004</v>
@@ -503,7 +508,7 @@
         <v>0.70499999999999996</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F5" s="1">
         <v>4.25</v>
@@ -514,7 +519,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>-0.73099999999999998</v>
@@ -523,7 +528,7 @@
         <v>0.69</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F6" s="1">
         <v>5.1920000000000002</v>
